--- a/academias/Lengua y Comunicación - Estadisticos 20232.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20232.xlsx
@@ -1083,25 +1083,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>43.3</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>62.1</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>37.9</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>21.7</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>115</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F6">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>34.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>35</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J10">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J11">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1430,25 +1430,25 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>192</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="F13">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>14.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1497,25 +1497,25 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1529,25 +1529,25 @@
         <v>12</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="F16">
-        <v>319</v>
+        <v>71</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>77.7</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>22.3</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1644,19 +1644,19 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="H2" s="1">
-        <v>40</v>
+        <v>43.3</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>48.3</v>
+        <v>62.1</v>
       </c>
       <c r="H3" s="1">
-        <v>51.7</v>
+        <v>37.9</v>
       </c>
       <c r="I3" s="2">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>56.5</v>
+        <v>78.3</v>
       </c>
       <c r="H4" s="1">
-        <v>43.5</v>
+        <v>21.7</v>
       </c>
       <c r="I4" s="2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>87.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="H5" s="1">
-        <v>12.1</v>
+        <v>33.3</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>115</v>
       </c>
       <c r="E6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
-        <v>64.3</v>
+        <v>65.2</v>
       </c>
       <c r="H6" s="1">
-        <v>35.7</v>
+        <v>34.8</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1816,19 +1816,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H7" s="1">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1886,19 +1886,19 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>77.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>22.6</v>
+        <v>16.1</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>35</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H10" s="1">
-        <v>22.9</v>
+        <v>14.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>54.2</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>45.8</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>38</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>86.8</v>
+        <v>94.7</v>
       </c>
       <c r="H12" s="1">
-        <v>13.2</v>
+        <v>5.3</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>192</v>
       </c>
       <c r="E13">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F13">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
-        <v>75.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>24.5</v>
+        <v>14.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2119,19 +2119,19 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="F16">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G16" s="1">
-        <v>71.5</v>
+        <v>77.7</v>
       </c>
       <c r="H16" s="1">
-        <v>28.5</v>
+        <v>22.3</v>
       </c>
       <c r="I16" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Lengua y Comunicación - Estadisticos 20232.xlsx
+++ b/academias/Lengua y Comunicación - Estadisticos 20232.xlsx
@@ -1644,19 +1644,19 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>56.7</v>
+        <v>76.7</v>
       </c>
       <c r="H2" s="1">
-        <v>43.3</v>
+        <v>23.3</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>62.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>37.9</v>
+        <v>6.9</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>78.3</v>
+        <v>87</v>
       </c>
       <c r="H4" s="1">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>66.7</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="1">
-        <v>33.3</v>
+        <v>18.2</v>
       </c>
       <c r="I5" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>115</v>
       </c>
       <c r="E6">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1">
-        <v>65.2</v>
+        <v>84.3</v>
       </c>
       <c r="H6" s="1">
-        <v>34.8</v>
+        <v>15.7</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1816,19 +1816,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H7" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1886,19 +1886,19 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>35</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>85.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>14.3</v>
+        <v>11.4</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>24</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2023,19 +2023,19 @@
         <v>192</v>
       </c>
       <c r="E13">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G13" s="1">
-        <v>85.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>14.6</v>
+        <v>9.4</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2119,19 +2119,19 @@
         <v>319</v>
       </c>
       <c r="E16">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="F16">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="G16" s="1">
-        <v>77.7</v>
+        <v>87.8</v>
       </c>
       <c r="H16" s="1">
-        <v>22.3</v>
+        <v>12.2</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
         <v>0</v>
